--- a/apiHirams/resources/templates/POTemplate.xlsx
+++ b/apiHirams/resources/templates/POTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5251198-EE21-4362-A5A8-A7149725DBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B2F8D0-5F4F-46E7-9FFB-E8D15B97BC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5391CC67-D73C-4521-B7F6-16F3EA47EC1F}"/>
   </bookViews>
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -845,6 +823,171 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -862,171 +1005,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1045,70 +1023,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1445,52 +1359,50 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="95" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+    </row>
+    <row r="3" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="36" t="s">
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="72"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67"/>
       <c r="F5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1501,85 +1413,85 @@
       <c r="I5" s="35"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="40" t="s">
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
     </row>
     <row r="7" spans="2:14" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="65" t="s">
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="68"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="87"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
+    </row>
+    <row r="9" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="78"/>
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="73"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="90"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="81"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="73"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="90"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="81"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="78"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="93"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" spans="2:14" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
       <c r="F14" s="27" t="s">
         <v>14</v>
       </c>
@@ -1595,101 +1507,101 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="29"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
       <c r="F15" s="30"/>
       <c r="G15" s="30"/>
       <c r="H15" s="31"/>
       <c r="I15" s="31"/>
     </row>
     <row r="16" spans="2:14" ht="4.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
     </row>
     <row r="17" spans="2:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89"/>
       <c r="H17" s="22" t="s">
         <v>6</v>
       </c>
       <c r="I17" s="32"/>
     </row>
     <row r="18" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48"/>
       <c r="H18" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="18"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="53"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="51"/>
       <c r="H19" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I19" s="33"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="56"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="61"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="59"/>
       <c r="H21" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="34"/>
     </row>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
     </row>
     <row r="23" spans="2:9" ht="6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="2:9" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1701,65 +1613,65 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="63"/>
+      <c r="C25" s="61"/>
       <c r="D25" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="63"/>
-      <c r="H25" s="64" t="s">
+      <c r="F25" s="61"/>
+      <c r="H25" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="I25" s="64"/>
+      <c r="I25" s="62"/>
     </row>
     <row r="26" spans="2:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="76"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="76" t="s">
+      <c r="E27" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="77" t="s">
+      <c r="B28" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="77"/>
+      <c r="C28" s="68"/>
       <c r="D28" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="77" t="s">
+      <c r="E28" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="43" t="s">
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="43"/>
+      <c r="I28" s="86"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="4"/>
@@ -1800,11 +1712,12 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I3"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="B12:E12"/>
@@ -1821,6 +1734,11 @@
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I3"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B20:G20"/>
@@ -1832,12 +1750,6 @@
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" display="hirams_supplies@yahoo.com" xr:uid="{E561545B-5732-499F-9190-7354C0FBD2B7}"/>
